--- a/Result/profitability/3515.xlsx
+++ b/Result/profitability/3515.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.67</v>
       </c>
       <c r="M2" t="n">
-        <v>3.4925</v>
+        <v>3.55</v>
       </c>
       <c r="N2" t="n">
-        <v>16.475</v>
+        <v>16.45875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>3.30625</v>
+        <v>3.255</v>
       </c>
       <c r="N3" t="n">
-        <v>16.0725</v>
+        <v>16.63625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.44</v>
       </c>
       <c r="M4" t="n">
-        <v>3.06625</v>
+        <v>2.9875</v>
       </c>
       <c r="N4" t="n">
-        <v>16.18875</v>
+        <v>16.83625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.29</v>
       </c>
       <c r="M5" t="n">
-        <v>2.78</v>
+        <v>2.73375</v>
       </c>
       <c r="N5" t="n">
-        <v>16.62625</v>
+        <v>17.39125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.91</v>
       </c>
       <c r="M6" t="n">
-        <v>2.60375</v>
+        <v>2.42875</v>
       </c>
       <c r="N6" t="n">
-        <v>17.19375</v>
+        <v>18.05625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>2.21</v>
       </c>
       <c r="M7" t="n">
-        <v>2.33625</v>
+        <v>2.20125</v>
       </c>
       <c r="N7" t="n">
-        <v>17.9975</v>
+        <v>18.895</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>2.2075</v>
+        <v>2.05875</v>
       </c>
       <c r="N8" t="n">
-        <v>19.125</v>
+        <v>19.75</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3515</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>10109</v>
+      </c>
+      <c r="D75" t="n">
+        <v>8091</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2017</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19.96</v>
+      </c>
+      <c r="G75" t="n">
+        <v>922</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.13%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>56</v>
+      </c>
+      <c r="J75" t="n">
+        <v>979</v>
+      </c>
+      <c r="K75" t="n">
+        <v>365</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.5275</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.615</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.28743961352657</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.3342245989304813</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.3699999999999997</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.1114457831325301</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>6.120000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.4421965317919077</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
